--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -257,9 +259,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -851,7 +850,7 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>23</v>
@@ -914,10 +913,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -925,10 +924,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -939,25 +938,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1008,13 +1007,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1023,15 +1022,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1054,13 +1053,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1099,19 +1098,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1123,7 +1122,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1131,10 +1130,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1142,10 +1141,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1157,16 +1156,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1216,13 +1215,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1231,15 +1230,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1250,7 +1249,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1262,13 +1261,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1319,22 +1318,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
